--- a/Soubhanik/checkupp_product_backlog_final.xlsx.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C99EEE-9FD0-41CC-B519-4128ADF77705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D6067E-2344-4249-8F1C-1274EB479829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2174,66 +2174,105 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2242,45 +2281,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2540,8 +2540,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
       <c r="C2" s="70"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
@@ -2553,14 +2553,14 @@
         <v>9</v>
       </c>
       <c r="G2" s="69"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="39">
+      <c r="A3" s="71">
         <v>1</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="71" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="30">
@@ -2586,8 +2586,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="71"/>
       <c r="C4" s="30">
         <v>1.2</v>
       </c>
@@ -2607,8 +2607,8 @@
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="71"/>
+      <c r="B5" s="71"/>
       <c r="C5" s="30">
         <v>1.3</v>
       </c>
@@ -2628,8 +2628,8 @@
       <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="71"/>
       <c r="C6" s="30">
         <v>1.4</v>
       </c>
@@ -2649,8 +2649,8 @@
       <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
       <c r="C7" s="30">
         <v>1.5</v>
       </c>
@@ -2740,80 +2740,80 @@
       <c r="H10" s="9"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" s="74" customFormat="1" ht="248.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="42" customFormat="1" ht="248.4" x14ac:dyDescent="0.3">
       <c r="A11" s="67"/>
       <c r="B11" s="67"/>
-      <c r="C11" s="71">
+      <c r="C11" s="39">
         <v>5.4</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="40" t="s">
         <v>277</v>
       </c>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="40" t="s">
         <v>279</v>
       </c>
-      <c r="G11" s="71" t="s">
+      <c r="G11" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="H11" s="73"/>
-      <c r="I11" s="72"/>
-    </row>
-    <row r="12" spans="1:9" s="74" customFormat="1" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="H11" s="41"/>
+      <c r="I11" s="40"/>
+    </row>
+    <row r="12" spans="1:9" s="42" customFormat="1" ht="179.4" x14ac:dyDescent="0.3">
       <c r="A12" s="68"/>
       <c r="B12" s="68"/>
-      <c r="C12" s="71">
+      <c r="C12" s="39">
         <v>5.5</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="D12" s="40" t="s">
         <v>274</v>
       </c>
-      <c r="E12" s="72" t="s">
+      <c r="E12" s="40" t="s">
         <v>278</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="G12" s="71" t="s">
+      <c r="G12" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="H12" s="73"/>
-      <c r="I12" s="72"/>
-    </row>
-    <row r="13" spans="1:9" s="74" customFormat="1" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="56">
+      <c r="H12" s="41"/>
+      <c r="I12" s="40"/>
+    </row>
+    <row r="13" spans="1:9" s="42" customFormat="1" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="43">
         <v>6</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="71">
+      <c r="C13" s="39">
         <v>6.1</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="D13" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="72" t="s">
+      <c r="E13" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="71" t="s">
+      <c r="G13" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="73" t="s">
+      <c r="H13" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="72" t="s">
+      <c r="I13" s="40" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="44"/>
       <c r="C14" s="11">
         <v>6.2</v>
       </c>
@@ -2833,8 +2833,8 @@
       <c r="I14" s="10"/>
     </row>
     <row r="15" spans="1:9" s="6" customFormat="1" ht="193.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="57"/>
-      <c r="B15" s="57"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
       <c r="C15" s="11">
         <v>6.3</v>
       </c>
@@ -2854,8 +2854,8 @@
       <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
-      <c r="B16" s="58"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="35">
         <v>6.4</v>
       </c>
@@ -2879,10 +2879,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A17" s="59">
+      <c r="A17" s="72">
         <v>7</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="43" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="11">
@@ -2908,8 +2908,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
-      <c r="B18" s="57"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="44"/>
       <c r="C18" s="11">
         <v>7.2</v>
       </c>
@@ -2931,8 +2931,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="60"/>
-      <c r="B19" s="57"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="44"/>
       <c r="C19" s="11">
         <v>7.3</v>
       </c>
@@ -2952,8 +2952,8 @@
       <c r="I19" s="10"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="193.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="61"/>
-      <c r="B20" s="58"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="45"/>
       <c r="C20" s="11">
         <v>7.4</v>
       </c>
@@ -3046,10 +3046,10 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="53">
+      <c r="A24" s="46">
         <v>12</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="46" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="16">
@@ -3075,8 +3075,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
-      <c r="B25" s="53"/>
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
       <c r="C25" s="16">
         <v>12.2</v>
       </c>
@@ -3100,8 +3100,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="53"/>
-      <c r="B26" s="53"/>
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
       <c r="C26" s="16">
         <v>12.3</v>
       </c>
@@ -3125,8 +3125,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A27" s="53"/>
-      <c r="B27" s="53"/>
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
       <c r="C27" s="16">
         <v>12.4</v>
       </c>
@@ -3150,8 +3150,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="53"/>
-      <c r="B28" s="53"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
       <c r="C28" s="16">
         <v>12.5</v>
       </c>
@@ -3175,10 +3175,10 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="54">
+      <c r="A29" s="47">
         <v>14</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="47" t="s">
         <v>84</v>
       </c>
       <c r="C29" s="18">
@@ -3204,8 +3204,8 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="54"/>
-      <c r="B30" s="54"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
       <c r="C30" s="18">
         <v>14.2</v>
       </c>
@@ -3229,8 +3229,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="54"/>
-      <c r="B31" s="54"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="47"/>
       <c r="C31" s="18">
         <v>14.3</v>
       </c>
@@ -3254,8 +3254,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="54"/>
-      <c r="B32" s="54"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="47"/>
       <c r="C32" s="18">
         <v>14.4</v>
       </c>
@@ -3279,8 +3279,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="54"/>
-      <c r="B33" s="54"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="47"/>
       <c r="C33" s="18">
         <v>14.5</v>
       </c>
@@ -3304,8 +3304,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="54"/>
-      <c r="B34" s="54"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="47"/>
       <c r="C34" s="18">
         <v>14.6</v>
       </c>
@@ -3329,8 +3329,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="54"/>
-      <c r="B35" s="54"/>
+      <c r="A35" s="47"/>
+      <c r="B35" s="47"/>
       <c r="C35" s="18">
         <v>14.7</v>
       </c>
@@ -3354,8 +3354,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="54"/>
-      <c r="B36" s="54"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="47"/>
       <c r="C36" s="18">
         <v>14.8</v>
       </c>
@@ -3379,8 +3379,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="54"/>
-      <c r="B37" s="54"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="47"/>
       <c r="C37" s="18">
         <v>14.9</v>
       </c>
@@ -3404,8 +3404,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="54"/>
-      <c r="B38" s="54"/>
+      <c r="A38" s="47"/>
+      <c r="B38" s="47"/>
       <c r="C38" s="18">
         <v>14.1</v>
       </c>
@@ -3429,8 +3429,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="54"/>
-      <c r="B39" s="54"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="47"/>
       <c r="C39" s="18">
         <v>14.11</v>
       </c>
@@ -3454,10 +3454,10 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="55">
+      <c r="A40" s="48">
         <v>15</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="48" t="s">
         <v>121</v>
       </c>
       <c r="C40" s="20">
@@ -3479,8 +3479,8 @@
       <c r="I40" s="19"/>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="47"/>
-      <c r="B41" s="47"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
       <c r="C41" s="20">
         <v>15.2</v>
       </c>
@@ -3500,8 +3500,8 @@
       <c r="I41" s="19"/>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="47"/>
-      <c r="B42" s="47"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
       <c r="C42" s="20">
         <v>15.3</v>
       </c>
@@ -3521,8 +3521,8 @@
       <c r="I42" s="19"/>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="47"/>
-      <c r="B43" s="47"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="49"/>
       <c r="C43" s="20">
         <v>15.4</v>
       </c>
@@ -3542,8 +3542,8 @@
       <c r="I43" s="19"/>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="47"/>
-      <c r="B44" s="47"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="49"/>
       <c r="C44" s="20">
         <v>15.5</v>
       </c>
@@ -3563,8 +3563,8 @@
       <c r="I44" s="19"/>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="47"/>
-      <c r="B45" s="47"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="49"/>
       <c r="C45" s="20">
         <v>15.6</v>
       </c>
@@ -3584,8 +3584,8 @@
       <c r="I45" s="19"/>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="47"/>
-      <c r="B46" s="47"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="49"/>
       <c r="C46" s="20">
         <v>15.7</v>
       </c>
@@ -3605,8 +3605,8 @@
       <c r="I46" s="19"/>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="47"/>
-      <c r="B47" s="47"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="49"/>
       <c r="C47" s="20">
         <v>15.8</v>
       </c>
@@ -3626,10 +3626,10 @@
       <c r="I47" s="19"/>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="46">
+      <c r="A48" s="56">
         <v>16</v>
       </c>
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="56" t="s">
         <v>140</v>
       </c>
       <c r="C48" s="36">
@@ -3655,8 +3655,8 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="46"/>
+      <c r="A49" s="56"/>
+      <c r="B49" s="56"/>
       <c r="C49" s="36">
         <v>16.2</v>
       </c>
@@ -3678,8 +3678,8 @@
       <c r="I49" s="21"/>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="46"/>
-      <c r="B50" s="46"/>
+      <c r="A50" s="56"/>
+      <c r="B50" s="56"/>
       <c r="C50" s="36">
         <v>16.3</v>
       </c>
@@ -3701,8 +3701,8 @@
       <c r="I50" s="21"/>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="46"/>
-      <c r="B51" s="46"/>
+      <c r="A51" s="56"/>
+      <c r="B51" s="56"/>
       <c r="C51" s="36">
         <v>16.399999999999999</v>
       </c>
@@ -3724,8 +3724,8 @@
       <c r="I51" s="21"/>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="46"/>
-      <c r="B52" s="46"/>
+      <c r="A52" s="56"/>
+      <c r="B52" s="56"/>
       <c r="C52" s="36">
         <v>16.5</v>
       </c>
@@ -3747,8 +3747,8 @@
       <c r="I52" s="21"/>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="47"/>
-      <c r="B53" s="47"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="49"/>
       <c r="C53" s="36">
         <v>16.600000000000001</v>
       </c>
@@ -3772,10 +3772,10 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="48">
+      <c r="A54" s="57">
         <v>17</v>
       </c>
-      <c r="B54" s="51" t="s">
+      <c r="B54" s="60" t="s">
         <v>157</v>
       </c>
       <c r="C54" s="24">
@@ -3799,8 +3799,8 @@
       <c r="I54" s="23"/>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="49"/>
-      <c r="B55" s="51"/>
+      <c r="A55" s="58"/>
+      <c r="B55" s="60"/>
       <c r="C55" s="24">
         <v>17.2</v>
       </c>
@@ -3822,8 +3822,8 @@
       <c r="I55" s="23"/>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="49"/>
-      <c r="B56" s="51"/>
+      <c r="A56" s="58"/>
+      <c r="B56" s="60"/>
       <c r="C56" s="24">
         <v>17.3</v>
       </c>
@@ -3845,8 +3845,8 @@
       <c r="I56" s="23"/>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="49"/>
-      <c r="B57" s="51"/>
+      <c r="A57" s="58"/>
+      <c r="B57" s="60"/>
       <c r="C57" s="24">
         <v>17.399999999999999</v>
       </c>
@@ -3868,8 +3868,8 @@
       <c r="I57" s="23"/>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="50"/>
-      <c r="B58" s="51"/>
+      <c r="A58" s="59"/>
+      <c r="B58" s="60"/>
       <c r="C58" s="24">
         <v>17.5</v>
       </c>
@@ -3891,10 +3891,10 @@
       <c r="I58" s="23"/>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="52">
+      <c r="A59" s="61">
         <v>18</v>
       </c>
-      <c r="B59" s="52" t="s">
+      <c r="B59" s="61" t="s">
         <v>170</v>
       </c>
       <c r="C59" s="8">
@@ -3920,8 +3920,8 @@
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="47"/>
-      <c r="B60" s="47"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="49"/>
       <c r="C60" s="8">
         <v>17.2</v>
       </c>
@@ -3945,8 +3945,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="47"/>
-      <c r="B61" s="47"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="49"/>
       <c r="C61" s="8">
         <v>17.3</v>
       </c>
@@ -3970,8 +3970,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="47"/>
-      <c r="B62" s="47"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
       <c r="C62" s="8">
         <v>17.399999999999999</v>
       </c>
@@ -3995,8 +3995,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="47"/>
-      <c r="B63" s="47"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="49"/>
       <c r="C63" s="8">
         <v>17.5</v>
       </c>
@@ -4020,8 +4020,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="47"/>
-      <c r="B64" s="47"/>
+      <c r="A64" s="49"/>
+      <c r="B64" s="49"/>
       <c r="C64" s="8">
         <v>17.600000000000001</v>
       </c>
@@ -4045,8 +4045,8 @@
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="47"/>
-      <c r="B65" s="47"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="49"/>
       <c r="C65" s="8">
         <v>17.7</v>
       </c>
@@ -4068,8 +4068,8 @@
       <c r="I65" s="7"/>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="47"/>
-      <c r="B66" s="47"/>
+      <c r="A66" s="49"/>
+      <c r="B66" s="49"/>
       <c r="C66" s="8">
         <v>17.8</v>
       </c>
@@ -4091,8 +4091,8 @@
       <c r="I66" s="7"/>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="47"/>
-      <c r="B67" s="47"/>
+      <c r="A67" s="49"/>
+      <c r="B67" s="49"/>
       <c r="C67" s="8">
         <v>17.899999999999999</v>
       </c>
@@ -4114,8 +4114,8 @@
       <c r="I67" s="7"/>
     </row>
     <row r="68" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="47"/>
-      <c r="B68" s="47"/>
+      <c r="A68" s="49"/>
+      <c r="B68" s="49"/>
       <c r="C68" s="8" t="s">
         <v>199</v>
       </c>
@@ -4139,10 +4139,10 @@
       </c>
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="40">
+      <c r="A69" s="50">
         <v>19</v>
       </c>
-      <c r="B69" s="43" t="s">
+      <c r="B69" s="53" t="s">
         <v>203</v>
       </c>
       <c r="C69" s="26">
@@ -4164,8 +4164,8 @@
       <c r="I69" s="32"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A70" s="41"/>
-      <c r="B70" s="44"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="54"/>
       <c r="C70" s="34">
         <v>19.2</v>
       </c>
@@ -4185,8 +4185,8 @@
       <c r="I70" s="32"/>
     </row>
     <row r="71" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="42"/>
-      <c r="B71" s="45"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="55"/>
       <c r="C71" s="34">
         <v>19.3</v>
       </c>
@@ -4204,10 +4204,10 @@
       <c r="I71" s="32"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="40">
+      <c r="A72" s="50">
         <v>20</v>
       </c>
-      <c r="B72" s="43" t="s">
+      <c r="B72" s="53" t="s">
         <v>213</v>
       </c>
       <c r="C72" s="26">
@@ -4229,8 +4229,8 @@
       <c r="I72" s="32"/>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A73" s="41"/>
-      <c r="B73" s="44"/>
+      <c r="A73" s="51"/>
+      <c r="B73" s="54"/>
       <c r="C73" s="34">
         <v>20.2</v>
       </c>
@@ -4253,8 +4253,8 @@
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="42"/>
-      <c r="B74" s="45"/>
+      <c r="A74" s="52"/>
+      <c r="B74" s="55"/>
       <c r="C74" s="26">
         <v>20.3</v>
       </c>
@@ -4273,10 +4273,10 @@
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="40">
+      <c r="A75" s="50">
         <v>21</v>
       </c>
-      <c r="B75" s="43" t="s">
+      <c r="B75" s="53" t="s">
         <v>221</v>
       </c>
       <c r="C75" s="26">
@@ -4298,8 +4298,8 @@
       <c r="I75" s="32"/>
     </row>
     <row r="76" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A76" s="41"/>
-      <c r="B76" s="44"/>
+      <c r="A76" s="51"/>
+      <c r="B76" s="54"/>
       <c r="C76" s="34">
         <v>21.2</v>
       </c>
@@ -4319,8 +4319,8 @@
       <c r="I76" s="32"/>
     </row>
     <row r="77" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="42"/>
-      <c r="B77" s="45"/>
+      <c r="A77" s="52"/>
+      <c r="B77" s="55"/>
       <c r="C77" s="26">
         <v>21.3</v>
       </c>
@@ -4336,10 +4336,10 @@
       <c r="I77" s="32"/>
     </row>
     <row r="78" spans="1:12" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="40">
+      <c r="A78" s="50">
         <v>22</v>
       </c>
-      <c r="B78" s="43" t="s">
+      <c r="B78" s="53" t="s">
         <v>229</v>
       </c>
       <c r="C78" s="26">
@@ -4361,8 +4361,8 @@
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="41"/>
-      <c r="B79" s="44"/>
+      <c r="A79" s="51"/>
+      <c r="B79" s="54"/>
       <c r="C79" s="34">
         <v>22.2</v>
       </c>
@@ -4382,8 +4382,8 @@
       <c r="I79" s="32"/>
     </row>
     <row r="80" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="42"/>
-      <c r="B80" s="45"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="55"/>
       <c r="C80" s="26">
         <v>22.3</v>
       </c>
@@ -4499,8 +4499,9 @@
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="A17:A20"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="A8:A12"/>
@@ -4510,6 +4511,10 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="B40:B47"/>
     <mergeCell ref="A75:A77"/>
     <mergeCell ref="B75:B77"/>
     <mergeCell ref="A78:A80"/>
@@ -4520,22 +4525,17 @@
     <mergeCell ref="B54:B58"/>
     <mergeCell ref="A59:A68"/>
     <mergeCell ref="B59:B68"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
     <mergeCell ref="A69:A71"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B17:B20"/>
     <mergeCell ref="A24:A28"/>
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="A29:A39"/>
     <mergeCell ref="B29:B39"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="B40:B47"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
